--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="D2">
-        <v>156</v>
+        <v>316</v>
       </c>
       <c r="E2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="D3">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G3">
-        <v>86</v>
+        <v>12</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Qwen3-Next-80B-A3B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D2">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -453,13 +453,13 @@
         <v>160</v>
       </c>
       <c r="D3">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3">
         <v>426</v>
